--- a/measurement/london_recording_manifest.xlsx
+++ b/measurement/london_recording_manifest.xlsx
@@ -509,7 +509,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Flat 12 Ashby Mews, Camden.</t>
+          <t>Flat 12, Ashby Mews, Camden.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Flat 2, Thornberry House, Islington, N1.</t>
+          <t>Flat 2, Thornberry House, Islington N1.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1216,20 +1216,20 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9 Colville Mews, Notting Hill, W1 1.</t>
+          <t>9 Colville Mews, Notting Hill, W11.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>S=1, D=0, I=1</t>
+          <t>S=0, D=0, I=0</t>
         </is>
       </c>
     </row>
@@ -1597,10 +1597,10 @@
         <v>0.65</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>-0.05000000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1613,10 +1613,10 @@
         <v>0.064445</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.08111</v>
+        <v>0.064445</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.016665</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>uk-london (34 keyterms)</t>
+          <t>uk-london (24 keyterms)</t>
         </is>
       </c>
     </row>
